--- a/PROPERTIES/SHANAYA/SHANAYA 2025.xlsx
+++ b/PROPERTIES/SHANAYA/SHANAYA 2025.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
@@ -15,6 +15,7 @@
     <sheet name="Sheet5" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="JUNE" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="JULY" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="AUG" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="132">
   <si>
     <t xml:space="preserve">COURTLAND REALTORS LTD P.O.BOX 11993, NAIROBI</t>
   </si>
@@ -407,21 +408,37 @@
   </si>
   <si>
     <t xml:space="preserve">MGNT COMM 5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DATE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TGV88JZ7LI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">31/07/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TH34PGRHS6 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TH40WHXXGE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* \-??_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* \-??_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="0"/>
     <numFmt numFmtId="168" formatCode="0.00"/>
     <numFmt numFmtId="169" formatCode="#,##0"/>
+    <numFmt numFmtId="170" formatCode="mm/dd/yy"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -604,6 +621,30 @@
       <family val="1"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="10.5"/>
+      <color rgb="FF008000"/>
+      <name val="Georgia"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Georgia"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color rgb="FF008000"/>
+      <name val="Georgia"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -688,7 +729,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="144">
+  <cellXfs count="157">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1262,6 +1303,58 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="169" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="25" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="27" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="27" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="27" fillId="5" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="27" fillId="3" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="27" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9609,4 +9702,1036 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:J69"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="78" width="8.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="78" width="26.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="78" width="17.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="78" width="11.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="78" width="31.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="78" width="13.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="78" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="78" width="17.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="78" width="32.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="18.11"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="79"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+    </row>
+    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="80" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
+    </row>
+    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="79"/>
+      <c r="B3" s="79"/>
+      <c r="C3" s="80" t="s">
+        <v>111</v>
+      </c>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="79"/>
+      <c r="I3" s="79" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="79"/>
+      <c r="B4" s="79"/>
+      <c r="C4" s="81" t="s">
+        <v>116</v>
+      </c>
+      <c r="D4" s="81"/>
+      <c r="E4" s="81"/>
+      <c r="F4" s="79"/>
+      <c r="G4" s="79"/>
+      <c r="H4" s="79"/>
+      <c r="I4" s="79"/>
+    </row>
+    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="80"/>
+      <c r="B5" s="80"/>
+      <c r="C5" s="80"/>
+      <c r="D5" s="82"/>
+      <c r="E5" s="82"/>
+      <c r="F5" s="82"/>
+      <c r="G5" s="82"/>
+      <c r="H5" s="82"/>
+      <c r="I5" s="83"/>
+    </row>
+    <row r="6" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="80" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="80" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="80" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="84" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="85" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="144" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="86" t="s">
+        <v>117</v>
+      </c>
+      <c r="H6" s="86" t="s">
+        <v>118</v>
+      </c>
+      <c r="I6" s="80" t="s">
+        <v>12</v>
+      </c>
+      <c r="J6" s="145" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="87" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="88" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="88" t="n">
+        <v>705567543</v>
+      </c>
+      <c r="D7" s="89" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E7" s="90"/>
+      <c r="F7" s="144"/>
+      <c r="G7" s="89" t="n">
+        <v>250</v>
+      </c>
+      <c r="H7" s="89" t="n">
+        <v>250</v>
+      </c>
+      <c r="I7" s="91"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="87" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="88" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="92" t="n">
+        <v>113717588</v>
+      </c>
+      <c r="D8" s="89" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E8" s="89"/>
+      <c r="F8" s="146"/>
+      <c r="G8" s="89" t="n">
+        <v>250</v>
+      </c>
+      <c r="H8" s="89"/>
+      <c r="I8" s="93" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="94" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="95" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="96" t="n">
+        <v>2348134216251</v>
+      </c>
+      <c r="D9" s="97" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E9" s="89"/>
+      <c r="F9" s="147"/>
+      <c r="G9" s="97" t="n">
+        <v>250</v>
+      </c>
+      <c r="H9" s="97"/>
+      <c r="I9" s="93"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="98" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="99" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="100"/>
+      <c r="D10" s="101" t="n">
+        <v>13000</v>
+      </c>
+      <c r="E10" s="102"/>
+      <c r="F10" s="148"/>
+      <c r="G10" s="103"/>
+      <c r="H10" s="103"/>
+      <c r="I10" s="98" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="104" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="88" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="92" t="n">
+        <v>724798762</v>
+      </c>
+      <c r="D11" s="89" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E11" s="89"/>
+      <c r="F11" s="146"/>
+      <c r="G11" s="89" t="n">
+        <v>250</v>
+      </c>
+      <c r="H11" s="89" t="n">
+        <v>250</v>
+      </c>
+      <c r="I11" s="88"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="105" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="106" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="107"/>
+      <c r="D12" s="108" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E12" s="108"/>
+      <c r="F12" s="149"/>
+      <c r="G12" s="108"/>
+      <c r="H12" s="108"/>
+      <c r="I12" s="109" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="110" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="88" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="92" t="n">
+        <v>768169176</v>
+      </c>
+      <c r="D13" s="89" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E13" s="111"/>
+      <c r="F13" s="146"/>
+      <c r="G13" s="89" t="n">
+        <v>250</v>
+      </c>
+      <c r="H13" s="89" t="n">
+        <v>250</v>
+      </c>
+      <c r="I13" s="88"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="79" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="112"/>
+      <c r="C14" s="113"/>
+      <c r="D14" s="114"/>
+      <c r="E14" s="114"/>
+      <c r="F14" s="150"/>
+      <c r="G14" s="114"/>
+      <c r="H14" s="114"/>
+      <c r="I14" s="85"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="79" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="115" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="113"/>
+      <c r="D15" s="114" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E15" s="114"/>
+      <c r="F15" s="150"/>
+      <c r="G15" s="114"/>
+      <c r="H15" s="114"/>
+      <c r="I15" s="116"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="79" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" s="112" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="113" t="n">
+        <v>720374242</v>
+      </c>
+      <c r="D16" s="114" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E16" s="114"/>
+      <c r="F16" s="150"/>
+      <c r="G16" s="114" t="n">
+        <v>250</v>
+      </c>
+      <c r="H16" s="114"/>
+      <c r="I16" s="117"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="87" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="88" t="s">
+        <v>119</v>
+      </c>
+      <c r="C17" s="92" t="n">
+        <v>715442786</v>
+      </c>
+      <c r="D17" s="89" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E17" s="89"/>
+      <c r="F17" s="146"/>
+      <c r="G17" s="89" t="n">
+        <v>250</v>
+      </c>
+      <c r="H17" s="89"/>
+      <c r="I17" s="93"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="87" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="88" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" s="92" t="n">
+        <v>712476390</v>
+      </c>
+      <c r="D18" s="89" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E18" s="89"/>
+      <c r="F18" s="146"/>
+      <c r="G18" s="89"/>
+      <c r="H18" s="89"/>
+      <c r="I18" s="91"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="79" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="112" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" s="113" t="n">
+        <v>796470291</v>
+      </c>
+      <c r="D19" s="114" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E19" s="89"/>
+      <c r="F19" s="150"/>
+      <c r="G19" s="114" t="n">
+        <v>250</v>
+      </c>
+      <c r="H19" s="114"/>
+      <c r="I19" s="117"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="87" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="88" t="s">
+        <v>95</v>
+      </c>
+      <c r="C20" s="118"/>
+      <c r="D20" s="119" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E20" s="114"/>
+      <c r="F20" s="151"/>
+      <c r="G20" s="118" t="n">
+        <v>250</v>
+      </c>
+      <c r="H20" s="118" t="n">
+        <v>250</v>
+      </c>
+      <c r="I20" s="120"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="94" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" s="95" t="s">
+        <v>96</v>
+      </c>
+      <c r="C21" s="96"/>
+      <c r="D21" s="97" t="n">
+        <v>12500</v>
+      </c>
+      <c r="E21" s="118"/>
+      <c r="F21" s="147"/>
+      <c r="G21" s="97" t="n">
+        <v>250</v>
+      </c>
+      <c r="H21" s="97"/>
+      <c r="I21" s="121"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="87" t="s">
+        <v>46</v>
+      </c>
+      <c r="B22" s="88" t="s">
+        <v>120</v>
+      </c>
+      <c r="C22" s="92"/>
+      <c r="D22" s="89" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E22" s="97"/>
+      <c r="F22" s="146"/>
+      <c r="G22" s="89" t="n">
+        <v>250</v>
+      </c>
+      <c r="H22" s="89"/>
+      <c r="I22" s="91"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="79" t="s">
+        <v>48</v>
+      </c>
+      <c r="B23" s="112" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" s="113" t="n">
+        <v>725513816</v>
+      </c>
+      <c r="D23" s="114" t="n">
+        <v>17000</v>
+      </c>
+      <c r="E23" s="114"/>
+      <c r="F23" s="150"/>
+      <c r="G23" s="114" t="n">
+        <v>250</v>
+      </c>
+      <c r="H23" s="114" t="n">
+        <v>250</v>
+      </c>
+      <c r="I23" s="122"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="79" t="s">
+        <v>50</v>
+      </c>
+      <c r="B24" s="112" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" s="113" t="n">
+        <v>716770298</v>
+      </c>
+      <c r="D24" s="114" t="n">
+        <v>16000</v>
+      </c>
+      <c r="E24" s="114"/>
+      <c r="F24" s="150"/>
+      <c r="G24" s="114" t="n">
+        <v>250</v>
+      </c>
+      <c r="H24" s="114" t="n">
+        <v>250</v>
+      </c>
+      <c r="I24" s="122"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="110" t="s">
+        <v>52</v>
+      </c>
+      <c r="B25" s="123" t="s">
+        <v>112</v>
+      </c>
+      <c r="C25" s="124" t="n">
+        <v>717865179</v>
+      </c>
+      <c r="D25" s="125" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E25" s="125"/>
+      <c r="F25" s="150" t="n">
+        <v>12500</v>
+      </c>
+      <c r="G25" s="126"/>
+      <c r="H25" s="126" t="n">
+        <v>250</v>
+      </c>
+      <c r="I25" s="127" t="s">
+        <v>128</v>
+      </c>
+      <c r="J25" s="0" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="79" t="s">
+        <v>54</v>
+      </c>
+      <c r="B26" s="112" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26" s="92" t="n">
+        <v>742242625</v>
+      </c>
+      <c r="D26" s="114" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E26" s="128"/>
+      <c r="F26" s="150"/>
+      <c r="G26" s="114" t="n">
+        <v>250</v>
+      </c>
+      <c r="H26" s="114" t="n">
+        <v>250</v>
+      </c>
+      <c r="I26" s="117"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="87" t="s">
+        <v>56</v>
+      </c>
+      <c r="B27" s="88" t="s">
+        <v>99</v>
+      </c>
+      <c r="C27" s="92" t="n">
+        <v>797627568</v>
+      </c>
+      <c r="D27" s="89" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E27" s="89"/>
+      <c r="F27" s="146" t="n">
+        <v>12500</v>
+      </c>
+      <c r="G27" s="89" t="n">
+        <v>250</v>
+      </c>
+      <c r="H27" s="89"/>
+      <c r="I27" s="87" t="s">
+        <v>130</v>
+      </c>
+      <c r="J27" s="152" t="n">
+        <v>45724</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="79" t="s">
+        <v>59</v>
+      </c>
+      <c r="B28" s="112" t="s">
+        <v>60</v>
+      </c>
+      <c r="C28" s="92" t="n">
+        <v>705296435</v>
+      </c>
+      <c r="D28" s="114" t="n">
+        <v>13000</v>
+      </c>
+      <c r="E28" s="114"/>
+      <c r="F28" s="150"/>
+      <c r="G28" s="114" t="n">
+        <v>250</v>
+      </c>
+      <c r="H28" s="114" t="n">
+        <v>250</v>
+      </c>
+      <c r="I28" s="122"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="87" t="s">
+        <v>62</v>
+      </c>
+      <c r="B29" s="88" t="s">
+        <v>17</v>
+      </c>
+      <c r="C29" s="92" t="n">
+        <v>718788066</v>
+      </c>
+      <c r="D29" s="89" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E29" s="114"/>
+      <c r="F29" s="146" t="n">
+        <v>12500</v>
+      </c>
+      <c r="G29" s="89" t="n">
+        <v>250</v>
+      </c>
+      <c r="H29" s="89"/>
+      <c r="I29" s="87"/>
+      <c r="J29" s="152" t="n">
+        <v>45785</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="87" t="s">
+        <v>64</v>
+      </c>
+      <c r="B30" s="88" t="s">
+        <v>65</v>
+      </c>
+      <c r="C30" s="92" t="n">
+        <v>705240836</v>
+      </c>
+      <c r="D30" s="89" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E30" s="89"/>
+      <c r="F30" s="146"/>
+      <c r="G30" s="89" t="n">
+        <v>250</v>
+      </c>
+      <c r="H30" s="89" t="n">
+        <v>250</v>
+      </c>
+      <c r="I30" s="129"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="79" t="s">
+        <v>66</v>
+      </c>
+      <c r="B31" s="112" t="s">
+        <v>67</v>
+      </c>
+      <c r="C31" s="130" t="n">
+        <v>721919440</v>
+      </c>
+      <c r="D31" s="131" t="n">
+        <v>13000</v>
+      </c>
+      <c r="E31" s="89"/>
+      <c r="F31" s="153"/>
+      <c r="G31" s="130" t="n">
+        <v>250</v>
+      </c>
+      <c r="H31" s="130" t="n">
+        <v>250</v>
+      </c>
+      <c r="I31" s="132" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="79" t="s">
+        <v>68</v>
+      </c>
+      <c r="B32" s="112" t="s">
+        <v>113</v>
+      </c>
+      <c r="C32" s="130" t="n">
+        <v>728695044</v>
+      </c>
+      <c r="D32" s="130" t="n">
+        <v>16000</v>
+      </c>
+      <c r="E32" s="130"/>
+      <c r="F32" s="153"/>
+      <c r="G32" s="130" t="n">
+        <v>250</v>
+      </c>
+      <c r="H32" s="130" t="n">
+        <v>250</v>
+      </c>
+      <c r="I32" s="79"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="79" t="s">
+        <v>70</v>
+      </c>
+      <c r="B33" s="112" t="s">
+        <v>71</v>
+      </c>
+      <c r="C33" s="133"/>
+      <c r="D33" s="130" t="n">
+        <v>17000</v>
+      </c>
+      <c r="E33" s="130"/>
+      <c r="F33" s="153"/>
+      <c r="G33" s="130" t="n">
+        <v>250</v>
+      </c>
+      <c r="H33" s="130" t="n">
+        <v>250</v>
+      </c>
+      <c r="I33" s="79"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="87" t="s">
+        <v>72</v>
+      </c>
+      <c r="B34" s="88" t="s">
+        <v>73</v>
+      </c>
+      <c r="C34" s="118"/>
+      <c r="D34" s="118" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E34" s="118"/>
+      <c r="F34" s="151"/>
+      <c r="G34" s="118" t="n">
+        <v>250</v>
+      </c>
+      <c r="H34" s="118"/>
+      <c r="I34" s="87"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="79" t="s">
+        <v>74</v>
+      </c>
+      <c r="B35" s="112" t="s">
+        <v>75</v>
+      </c>
+      <c r="C35" s="130" t="n">
+        <v>716805780</v>
+      </c>
+      <c r="D35" s="130" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E35" s="130"/>
+      <c r="F35" s="153"/>
+      <c r="G35" s="130" t="n">
+        <v>250</v>
+      </c>
+      <c r="H35" s="130"/>
+      <c r="I35" s="79"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="79" t="s">
+        <v>76</v>
+      </c>
+      <c r="B36" s="112" t="s">
+        <v>101</v>
+      </c>
+      <c r="C36" s="130" t="n">
+        <v>729249813</v>
+      </c>
+      <c r="D36" s="130" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E36" s="130"/>
+      <c r="F36" s="153"/>
+      <c r="G36" s="130" t="n">
+        <v>250</v>
+      </c>
+      <c r="H36" s="130"/>
+      <c r="I36" s="79"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="79" t="s">
+        <v>77</v>
+      </c>
+      <c r="B37" s="112" t="s">
+        <v>102</v>
+      </c>
+      <c r="C37" s="130" t="n">
+        <v>711926938</v>
+      </c>
+      <c r="D37" s="130" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E37" s="130"/>
+      <c r="F37" s="153" t="n">
+        <v>17000</v>
+      </c>
+      <c r="G37" s="130" t="n">
+        <v>250</v>
+      </c>
+      <c r="H37" s="130" t="n">
+        <v>250</v>
+      </c>
+      <c r="I37" s="79" t="s">
+        <v>131</v>
+      </c>
+      <c r="J37" s="152" t="n">
+        <v>45755</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="79" t="s">
+        <v>79</v>
+      </c>
+      <c r="B38" s="112" t="s">
+        <v>80</v>
+      </c>
+      <c r="C38" s="130" t="n">
+        <v>703211387</v>
+      </c>
+      <c r="D38" s="130" t="n">
+        <v>12500</v>
+      </c>
+      <c r="E38" s="130"/>
+      <c r="F38" s="154"/>
+      <c r="G38" s="134" t="n">
+        <v>250</v>
+      </c>
+      <c r="H38" s="135"/>
+      <c r="I38" s="79"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="98" t="s">
+        <v>81</v>
+      </c>
+      <c r="B39" s="136" t="s">
+        <v>114</v>
+      </c>
+      <c r="C39" s="137" t="n">
+        <v>729808848</v>
+      </c>
+      <c r="D39" s="137" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E39" s="137"/>
+      <c r="F39" s="155"/>
+      <c r="G39" s="137" t="n">
+        <v>250</v>
+      </c>
+      <c r="H39" s="137"/>
+      <c r="I39" s="98" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="79" t="s">
+        <v>83</v>
+      </c>
+      <c r="B40" s="112" t="s">
+        <v>103</v>
+      </c>
+      <c r="C40" s="130" t="n">
+        <v>722648411</v>
+      </c>
+      <c r="D40" s="130" t="n">
+        <v>12500</v>
+      </c>
+      <c r="E40" s="130"/>
+      <c r="F40" s="153"/>
+      <c r="G40" s="130" t="n">
+        <v>250</v>
+      </c>
+      <c r="H40" s="130" t="n">
+        <v>250</v>
+      </c>
+      <c r="I40" s="79"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="79" t="s">
+        <v>84</v>
+      </c>
+      <c r="B41" s="112" t="s">
+        <v>85</v>
+      </c>
+      <c r="C41" s="130" t="n">
+        <v>727104429</v>
+      </c>
+      <c r="D41" s="130" t="n">
+        <v>17500</v>
+      </c>
+      <c r="E41" s="130"/>
+      <c r="F41" s="153"/>
+      <c r="G41" s="130" t="n">
+        <v>250</v>
+      </c>
+      <c r="H41" s="130" t="n">
+        <v>250</v>
+      </c>
+      <c r="I41" s="79"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="79" t="s">
+        <v>86</v>
+      </c>
+      <c r="B42" s="112" t="s">
+        <v>121</v>
+      </c>
+      <c r="C42" s="130" t="n">
+        <v>757112245</v>
+      </c>
+      <c r="D42" s="130" t="n">
+        <v>18000</v>
+      </c>
+      <c r="E42" s="130"/>
+      <c r="F42" s="153"/>
+      <c r="G42" s="130" t="n">
+        <v>250</v>
+      </c>
+      <c r="H42" s="130" t="n">
+        <v>250</v>
+      </c>
+      <c r="I42" s="79"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="79"/>
+      <c r="B43" s="130"/>
+      <c r="C43" s="130"/>
+      <c r="D43" s="138" t="n">
+        <v>455250</v>
+      </c>
+      <c r="E43" s="138"/>
+      <c r="F43" s="156" t="n">
+        <f aca="false">SUM(F7:F42)</f>
+        <v>54500</v>
+      </c>
+      <c r="G43" s="138" t="n">
+        <v>8000</v>
+      </c>
+      <c r="H43" s="138" t="n">
+        <v>4250</v>
+      </c>
+      <c r="I43" s="79"/>
+    </row>
+    <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D44" s="139"/>
+      <c r="E44" s="139"/>
+      <c r="F44" s="139"/>
+      <c r="G44" s="139"/>
+      <c r="H44" s="139"/>
+    </row>
+    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D45" s="139"/>
+      <c r="E45" s="139"/>
+      <c r="F45" s="139"/>
+      <c r="G45" s="139"/>
+      <c r="H45" s="139"/>
+    </row>
+    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D46" s="140"/>
+      <c r="E46" s="141"/>
+      <c r="F46" s="140"/>
+      <c r="G46" s="140"/>
+      <c r="H46" s="140"/>
+    </row>
+    <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B47" s="78" t="s">
+        <v>122</v>
+      </c>
+      <c r="D47" s="140"/>
+      <c r="E47" s="141"/>
+      <c r="F47" s="140"/>
+      <c r="G47" s="140"/>
+      <c r="H47" s="140"/>
+    </row>
+    <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B48" s="78" t="s">
+        <v>123</v>
+      </c>
+      <c r="D48" s="140"/>
+      <c r="E48" s="141"/>
+      <c r="F48" s="140"/>
+      <c r="G48" s="140"/>
+      <c r="H48" s="140"/>
+    </row>
+    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B49" s="78" t="s">
+        <v>124</v>
+      </c>
+      <c r="D49" s="140"/>
+      <c r="E49" s="141"/>
+      <c r="F49" s="140"/>
+      <c r="G49" s="140"/>
+      <c r="H49" s="140"/>
+    </row>
+    <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D50" s="141"/>
+    </row>
+    <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B52" s="142" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B53" s="78" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B54" s="78" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B55" s="78" t="s">
+        <v>90</v>
+      </c>
+      <c r="E55" s="143"/>
+    </row>
+    <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B56" s="78" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>
--- a/PROPERTIES/SHANAYA/SHANAYA 2025.xlsx
+++ b/PROPERTIES/SHANAYA/SHANAYA 2025.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="133">
   <si>
     <t xml:space="preserve">COURTLAND REALTORS LTD P.O.BOX 11993, NAIROBI</t>
   </si>
@@ -411,6 +411,9 @@
   </si>
   <si>
     <t xml:space="preserve">DATE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TH41WJOYE3</t>
   </si>
   <si>
     <t xml:space="preserve">TGV88JZ7LI </t>
@@ -1310,7 +1313,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1338,7 +1341,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9721,7 +9724,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="78" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="78" width="17.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="78" width="32.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="18.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="18.11"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9821,7 +9824,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="87" t="s">
         <v>13</v>
       </c>
@@ -10157,14 +10160,21 @@
         <v>17000</v>
       </c>
       <c r="E23" s="114"/>
-      <c r="F23" s="150"/>
+      <c r="F23" s="150" t="n">
+        <v>17500</v>
+      </c>
       <c r="G23" s="114" t="n">
         <v>250</v>
       </c>
       <c r="H23" s="114" t="n">
         <v>250</v>
       </c>
-      <c r="I23" s="122"/>
+      <c r="I23" s="122" t="s">
+        <v>128</v>
+      </c>
+      <c r="J23" s="152" t="n">
+        <v>45755</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="79" t="s">
@@ -10211,10 +10221,10 @@
         <v>250</v>
       </c>
       <c r="I25" s="127" t="s">
-        <v>128</v>
-      </c>
-      <c r="J25" s="0" t="s">
         <v>129</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10262,7 +10272,7 @@
       </c>
       <c r="H27" s="89"/>
       <c r="I27" s="87" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J27" s="152" t="n">
         <v>45724</v>
@@ -10494,7 +10504,7 @@
         <v>250</v>
       </c>
       <c r="I37" s="79" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J37" s="152" t="n">
         <v>45755</v>
@@ -10623,7 +10633,7 @@
       <c r="E43" s="138"/>
       <c r="F43" s="156" t="n">
         <f aca="false">SUM(F7:F42)</f>
-        <v>54500</v>
+        <v>72000</v>
       </c>
       <c r="G43" s="138" t="n">
         <v>8000</v>

--- a/PROPERTIES/SHANAYA/SHANAYA 2025.xlsx
+++ b/PROPERTIES/SHANAYA/SHANAYA 2025.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="963" uniqueCount="134">
   <si>
     <t xml:space="preserve">COURTLAND REALTORS LTD P.O.BOX 11993, NAIROBI</t>
   </si>
@@ -414,6 +414,9 @@
   </si>
   <si>
     <t xml:space="preserve">TH41WJOYE3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TH73E9SVMJ </t>
   </si>
   <si>
     <t xml:space="preserve">TGV88JZ7LI </t>
@@ -10190,14 +10193,21 @@
         <v>16000</v>
       </c>
       <c r="E24" s="114"/>
-      <c r="F24" s="150"/>
+      <c r="F24" s="150" t="n">
+        <v>18000</v>
+      </c>
       <c r="G24" s="114" t="n">
         <v>250</v>
       </c>
       <c r="H24" s="114" t="n">
         <v>250</v>
       </c>
-      <c r="I24" s="122"/>
+      <c r="I24" s="122" t="s">
+        <v>129</v>
+      </c>
+      <c r="J24" s="152" t="n">
+        <v>45846</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="110" t="s">
@@ -10221,10 +10231,10 @@
         <v>250</v>
       </c>
       <c r="I25" s="127" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10272,7 +10282,7 @@
       </c>
       <c r="H27" s="89"/>
       <c r="I27" s="87" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J27" s="152" t="n">
         <v>45724</v>
@@ -10504,7 +10514,7 @@
         <v>250</v>
       </c>
       <c r="I37" s="79" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J37" s="152" t="n">
         <v>45755</v>
@@ -10633,7 +10643,7 @@
       <c r="E43" s="138"/>
       <c r="F43" s="156" t="n">
         <f aca="false">SUM(F7:F42)</f>
-        <v>72000</v>
+        <v>90000</v>
       </c>
       <c r="G43" s="138" t="n">
         <v>8000</v>

--- a/PROPERTIES/SHANAYA/SHANAYA 2025.xlsx
+++ b/PROPERTIES/SHANAYA/SHANAYA 2025.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="963" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="964" uniqueCount="136">
   <si>
     <t xml:space="preserve">COURTLAND REALTORS LTD P.O.BOX 11993, NAIROBI</t>
   </si>
@@ -411,6 +411,12 @@
   </si>
   <si>
     <t xml:space="preserve">DATE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BALANCE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUNGEI</t>
   </si>
   <si>
     <t xml:space="preserve">TH41WJOYE3</t>
@@ -444,7 +450,7 @@
     <numFmt numFmtId="169" formatCode="#,##0"/>
     <numFmt numFmtId="170" formatCode="mm/dd/yy"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -645,8 +651,40 @@
     </font>
     <font>
       <b val="true"/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="12"/>
       <color rgb="FF008000"/>
+      <name val="Georgia"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Georgia"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="13"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="13"/>
+      <color rgb="FFFF0000"/>
       <name val="Georgia"/>
       <family val="1"/>
       <charset val="1"/>
@@ -735,7 +773,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="157">
+  <cellXfs count="163">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1320,47 +1358,71 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="27" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="27" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="28" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="28" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="28" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="27" fillId="5" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="27" fillId="3" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="27" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="28" fillId="5" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="28" fillId="3" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="28" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9715,7 +9777,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J69"/>
+  <dimension ref="A1:K69"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="78" width="8.54"/>
@@ -9728,6 +9790,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="78" width="17.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="78" width="32.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="18.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="14.63"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9826,8 +9889,11 @@
       <c r="J6" s="145" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K6" s="146" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="87" t="s">
         <v>13</v>
       </c>
@@ -9841,7 +9907,9 @@
         <v>10000</v>
       </c>
       <c r="E7" s="90"/>
-      <c r="F7" s="144"/>
+      <c r="F7" s="147" t="n">
+        <v>10000</v>
+      </c>
       <c r="G7" s="89" t="n">
         <v>250</v>
       </c>
@@ -9849,8 +9917,10 @@
         <v>250</v>
       </c>
       <c r="I7" s="91"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J7" s="148"/>
+      <c r="K7" s="149"/>
+    </row>
+    <row r="8" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="87" t="s">
         <v>16</v>
       </c>
@@ -9864,16 +9934,22 @@
         <v>10000</v>
       </c>
       <c r="E8" s="89"/>
-      <c r="F8" s="146"/>
+      <c r="F8" s="150" t="n">
+        <v>10000</v>
+      </c>
       <c r="G8" s="89" t="n">
         <v>250</v>
       </c>
-      <c r="H8" s="89"/>
+      <c r="H8" s="89" t="n">
+        <v>250</v>
+      </c>
       <c r="I8" s="93" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J8" s="148"/>
+      <c r="K8" s="149"/>
+    </row>
+    <row r="9" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="94" t="s">
         <v>19</v>
       </c>
@@ -9887,14 +9963,16 @@
         <v>10000</v>
       </c>
       <c r="E9" s="89"/>
-      <c r="F9" s="147"/>
-      <c r="G9" s="97" t="n">
-        <v>250</v>
-      </c>
+      <c r="F9" s="151"/>
+      <c r="G9" s="97"/>
       <c r="H9" s="97"/>
       <c r="I9" s="93"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J9" s="148"/>
+      <c r="K9" s="152" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="98" t="s">
         <v>20</v>
       </c>
@@ -9906,14 +9984,16 @@
         <v>13000</v>
       </c>
       <c r="E10" s="102"/>
-      <c r="F10" s="148"/>
+      <c r="F10" s="153"/>
       <c r="G10" s="103"/>
       <c r="H10" s="103"/>
       <c r="I10" s="98" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J10" s="148"/>
+      <c r="K10" s="152"/>
+    </row>
+    <row r="11" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="104" t="s">
         <v>23</v>
       </c>
@@ -9927,7 +10007,9 @@
         <v>11000</v>
       </c>
       <c r="E11" s="89"/>
-      <c r="F11" s="146"/>
+      <c r="F11" s="150" t="n">
+        <v>11000</v>
+      </c>
       <c r="G11" s="89" t="n">
         <v>250</v>
       </c>
@@ -9935,8 +10017,10 @@
         <v>250</v>
       </c>
       <c r="I11" s="88"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J11" s="148"/>
+      <c r="K11" s="152"/>
+    </row>
+    <row r="12" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="105" t="s">
         <v>25</v>
       </c>
@@ -9948,14 +10032,16 @@
         <v>11000</v>
       </c>
       <c r="E12" s="108"/>
-      <c r="F12" s="149"/>
+      <c r="F12" s="154"/>
       <c r="G12" s="108"/>
       <c r="H12" s="108"/>
       <c r="I12" s="109" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J12" s="148"/>
+      <c r="K12" s="152"/>
+    </row>
+    <row r="13" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="110" t="s">
         <v>27</v>
       </c>
@@ -9969,7 +10055,9 @@
         <v>11000</v>
       </c>
       <c r="E13" s="111"/>
-      <c r="F13" s="146"/>
+      <c r="F13" s="150" t="n">
+        <v>11000</v>
+      </c>
       <c r="G13" s="89" t="n">
         <v>250</v>
       </c>
@@ -9977,21 +10065,35 @@
         <v>250</v>
       </c>
       <c r="I13" s="88"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J13" s="148"/>
+      <c r="K13" s="152"/>
+    </row>
+    <row r="14" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="79" t="s">
         <v>29</v>
       </c>
       <c r="B14" s="112"/>
-      <c r="C14" s="113"/>
-      <c r="D14" s="114"/>
+      <c r="C14" s="113" t="n">
+        <v>711926938</v>
+      </c>
+      <c r="D14" s="114" t="n">
+        <v>16000</v>
+      </c>
       <c r="E14" s="114"/>
-      <c r="F14" s="150"/>
-      <c r="G14" s="114"/>
-      <c r="H14" s="114"/>
+      <c r="F14" s="155" t="n">
+        <v>16000</v>
+      </c>
+      <c r="G14" s="114" t="n">
+        <v>250</v>
+      </c>
+      <c r="H14" s="114" t="n">
+        <v>250</v>
+      </c>
       <c r="I14" s="85"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J14" s="148"/>
+      <c r="K14" s="152"/>
+    </row>
+    <row r="15" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="79" t="s">
         <v>31</v>
       </c>
@@ -10003,12 +10105,16 @@
         <v>10000</v>
       </c>
       <c r="E15" s="114"/>
-      <c r="F15" s="150"/>
+      <c r="F15" s="155"/>
       <c r="G15" s="114"/>
       <c r="H15" s="114"/>
       <c r="I15" s="116"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J15" s="148"/>
+      <c r="K15" s="152" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="79" t="s">
         <v>33</v>
       </c>
@@ -10022,14 +10128,20 @@
         <v>12000</v>
       </c>
       <c r="E16" s="114"/>
-      <c r="F16" s="150"/>
+      <c r="F16" s="155" t="n">
+        <v>12000</v>
+      </c>
       <c r="G16" s="114" t="n">
         <v>250</v>
       </c>
-      <c r="H16" s="114"/>
+      <c r="H16" s="114" t="n">
+        <v>250</v>
+      </c>
       <c r="I16" s="117"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J16" s="148"/>
+      <c r="K16" s="152"/>
+    </row>
+    <row r="17" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="87" t="s">
         <v>35</v>
       </c>
@@ -10043,14 +10155,20 @@
         <v>12000</v>
       </c>
       <c r="E17" s="89"/>
-      <c r="F17" s="146"/>
+      <c r="F17" s="150" t="n">
+        <v>12000</v>
+      </c>
       <c r="G17" s="89" t="n">
         <v>250</v>
       </c>
-      <c r="H17" s="89"/>
+      <c r="H17" s="89" t="n">
+        <v>250</v>
+      </c>
       <c r="I17" s="93"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J17" s="148"/>
+      <c r="K17" s="152"/>
+    </row>
+    <row r="18" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="87" t="s">
         <v>37</v>
       </c>
@@ -10064,12 +10182,20 @@
         <v>12000</v>
       </c>
       <c r="E18" s="89"/>
-      <c r="F18" s="146"/>
-      <c r="G18" s="89"/>
-      <c r="H18" s="89"/>
+      <c r="F18" s="150" t="n">
+        <v>12000</v>
+      </c>
+      <c r="G18" s="89" t="n">
+        <v>250</v>
+      </c>
+      <c r="H18" s="89" t="n">
+        <v>250</v>
+      </c>
       <c r="I18" s="91"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J18" s="148"/>
+      <c r="K18" s="152"/>
+    </row>
+    <row r="19" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="79" t="s">
         <v>40</v>
       </c>
@@ -10083,26 +10209,36 @@
         <v>12000</v>
       </c>
       <c r="E19" s="89"/>
-      <c r="F19" s="150"/>
+      <c r="F19" s="155" t="n">
+        <v>12000</v>
+      </c>
       <c r="G19" s="114" t="n">
         <v>250</v>
       </c>
-      <c r="H19" s="114"/>
+      <c r="H19" s="114" t="n">
+        <v>250</v>
+      </c>
       <c r="I19" s="117"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J19" s="148"/>
+      <c r="K19" s="152"/>
+    </row>
+    <row r="20" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="87" t="s">
         <v>42</v>
       </c>
       <c r="B20" s="88" t="s">
-        <v>95</v>
-      </c>
-      <c r="C20" s="118"/>
+        <v>129</v>
+      </c>
+      <c r="C20" s="118" t="n">
+        <v>726948690</v>
+      </c>
       <c r="D20" s="119" t="n">
         <v>12000</v>
       </c>
       <c r="E20" s="114"/>
-      <c r="F20" s="151"/>
+      <c r="F20" s="156" t="n">
+        <v>12000</v>
+      </c>
       <c r="G20" s="118" t="n">
         <v>250</v>
       </c>
@@ -10110,27 +10246,37 @@
         <v>250</v>
       </c>
       <c r="I20" s="120"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J20" s="148"/>
+      <c r="K20" s="152"/>
+    </row>
+    <row r="21" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="94" t="s">
         <v>44</v>
       </c>
       <c r="B21" s="95" t="s">
         <v>96</v>
       </c>
-      <c r="C21" s="96"/>
+      <c r="C21" s="96" t="n">
+        <v>700278925</v>
+      </c>
       <c r="D21" s="97" t="n">
         <v>12500</v>
       </c>
       <c r="E21" s="118"/>
-      <c r="F21" s="147"/>
+      <c r="F21" s="151" t="n">
+        <v>12000</v>
+      </c>
       <c r="G21" s="97" t="n">
         <v>250</v>
       </c>
-      <c r="H21" s="97"/>
+      <c r="H21" s="97" t="n">
+        <v>250</v>
+      </c>
       <c r="I21" s="121"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J21" s="148"/>
+      <c r="K21" s="152"/>
+    </row>
+    <row r="22" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="87" t="s">
         <v>46</v>
       </c>
@@ -10142,14 +10288,16 @@
         <v>12000</v>
       </c>
       <c r="E22" s="97"/>
-      <c r="F22" s="146"/>
-      <c r="G22" s="89" t="n">
-        <v>250</v>
-      </c>
+      <c r="F22" s="150" t="n">
+        <v>12000</v>
+      </c>
+      <c r="G22" s="89"/>
       <c r="H22" s="89"/>
       <c r="I22" s="91"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J22" s="148"/>
+      <c r="K22" s="152"/>
+    </row>
+    <row r="23" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="79" t="s">
         <v>48</v>
       </c>
@@ -10163,7 +10311,7 @@
         <v>17000</v>
       </c>
       <c r="E23" s="114"/>
-      <c r="F23" s="150" t="n">
+      <c r="F23" s="155" t="n">
         <v>17500</v>
       </c>
       <c r="G23" s="114" t="n">
@@ -10173,13 +10321,14 @@
         <v>250</v>
       </c>
       <c r="I23" s="122" t="s">
-        <v>128</v>
-      </c>
-      <c r="J23" s="152" t="n">
+        <v>130</v>
+      </c>
+      <c r="J23" s="157" t="n">
         <v>45755</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K23" s="152"/>
+    </row>
+    <row r="24" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="79" t="s">
         <v>50</v>
       </c>
@@ -10193,7 +10342,7 @@
         <v>16000</v>
       </c>
       <c r="E24" s="114"/>
-      <c r="F24" s="150" t="n">
+      <c r="F24" s="155" t="n">
         <v>18000</v>
       </c>
       <c r="G24" s="114" t="n">
@@ -10203,13 +10352,14 @@
         <v>250</v>
       </c>
       <c r="I24" s="122" t="s">
-        <v>129</v>
-      </c>
-      <c r="J24" s="152" t="n">
+        <v>131</v>
+      </c>
+      <c r="J24" s="157" t="n">
         <v>45846</v>
       </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K24" s="152"/>
+    </row>
+    <row r="25" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="110" t="s">
         <v>52</v>
       </c>
@@ -10223,21 +10373,24 @@
         <v>12000</v>
       </c>
       <c r="E25" s="125"/>
-      <c r="F25" s="150" t="n">
+      <c r="F25" s="155" t="n">
         <v>12500</v>
       </c>
-      <c r="G25" s="126"/>
-      <c r="H25" s="126" t="n">
+      <c r="G25" s="125" t="n">
+        <v>250</v>
+      </c>
+      <c r="H25" s="125" t="n">
         <v>250</v>
       </c>
       <c r="I25" s="127" t="s">
-        <v>130</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>132</v>
+      </c>
+      <c r="J25" s="158" t="s">
+        <v>133</v>
+      </c>
+      <c r="K25" s="152"/>
+    </row>
+    <row r="26" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="79" t="s">
         <v>54</v>
       </c>
@@ -10251,7 +10404,9 @@
         <v>12000</v>
       </c>
       <c r="E26" s="128"/>
-      <c r="F26" s="150"/>
+      <c r="F26" s="155" t="n">
+        <v>6000</v>
+      </c>
       <c r="G26" s="114" t="n">
         <v>250</v>
       </c>
@@ -10259,8 +10414,10 @@
         <v>250</v>
       </c>
       <c r="I26" s="117"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J26" s="148"/>
+      <c r="K26" s="152"/>
+    </row>
+    <row r="27" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="87" t="s">
         <v>56</v>
       </c>
@@ -10274,21 +10431,24 @@
         <v>12000</v>
       </c>
       <c r="E27" s="89"/>
-      <c r="F27" s="146" t="n">
+      <c r="F27" s="150" t="n">
         <v>12500</v>
       </c>
       <c r="G27" s="89" t="n">
         <v>250</v>
       </c>
-      <c r="H27" s="89"/>
+      <c r="H27" s="89" t="n">
+        <v>250</v>
+      </c>
       <c r="I27" s="87" t="s">
-        <v>132</v>
-      </c>
-      <c r="J27" s="152" t="n">
+        <v>134</v>
+      </c>
+      <c r="J27" s="157" t="n">
         <v>45724</v>
       </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K27" s="152"/>
+    </row>
+    <row r="28" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="79" t="s">
         <v>59</v>
       </c>
@@ -10299,10 +10459,12 @@
         <v>705296435</v>
       </c>
       <c r="D28" s="114" t="n">
-        <v>13000</v>
+        <v>12500</v>
       </c>
       <c r="E28" s="114"/>
-      <c r="F28" s="150"/>
+      <c r="F28" s="155" t="n">
+        <v>12500</v>
+      </c>
       <c r="G28" s="114" t="n">
         <v>250</v>
       </c>
@@ -10310,8 +10472,10 @@
         <v>250</v>
       </c>
       <c r="I28" s="122"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J28" s="148"/>
+      <c r="K28" s="152"/>
+    </row>
+    <row r="29" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="87" t="s">
         <v>62</v>
       </c>
@@ -10325,19 +10489,22 @@
         <v>12000</v>
       </c>
       <c r="E29" s="114"/>
-      <c r="F29" s="146" t="n">
+      <c r="F29" s="150" t="n">
         <v>12500</v>
       </c>
       <c r="G29" s="89" t="n">
         <v>250</v>
       </c>
-      <c r="H29" s="89"/>
+      <c r="H29" s="89" t="n">
+        <v>250</v>
+      </c>
       <c r="I29" s="87"/>
-      <c r="J29" s="152" t="n">
+      <c r="J29" s="157" t="n">
         <v>45785</v>
       </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K29" s="152"/>
+    </row>
+    <row r="30" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="87" t="s">
         <v>64</v>
       </c>
@@ -10351,16 +10518,16 @@
         <v>12000</v>
       </c>
       <c r="E30" s="89"/>
-      <c r="F30" s="146"/>
-      <c r="G30" s="89" t="n">
-        <v>250</v>
-      </c>
-      <c r="H30" s="89" t="n">
-        <v>250</v>
-      </c>
+      <c r="F30" s="150"/>
+      <c r="G30" s="89"/>
+      <c r="H30" s="89"/>
       <c r="I30" s="129"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J30" s="148"/>
+      <c r="K30" s="152" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="79" t="s">
         <v>66</v>
       </c>
@@ -10374,7 +10541,9 @@
         <v>13000</v>
       </c>
       <c r="E31" s="89"/>
-      <c r="F31" s="153"/>
+      <c r="F31" s="159" t="n">
+        <v>12500</v>
+      </c>
       <c r="G31" s="130" t="n">
         <v>250</v>
       </c>
@@ -10384,8 +10553,10 @@
       <c r="I31" s="132" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J31" s="148"/>
+      <c r="K31" s="152"/>
+    </row>
+    <row r="32" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="79" t="s">
         <v>68</v>
       </c>
@@ -10399,7 +10570,9 @@
         <v>16000</v>
       </c>
       <c r="E32" s="130"/>
-      <c r="F32" s="153"/>
+      <c r="F32" s="159" t="n">
+        <v>16000</v>
+      </c>
       <c r="G32" s="130" t="n">
         <v>250</v>
       </c>
@@ -10407,20 +10580,26 @@
         <v>250</v>
       </c>
       <c r="I32" s="79"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J32" s="148"/>
+      <c r="K32" s="152"/>
+    </row>
+    <row r="33" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="79" t="s">
         <v>70</v>
       </c>
       <c r="B33" s="112" t="s">
         <v>71</v>
       </c>
-      <c r="C33" s="133"/>
+      <c r="C33" s="133" t="n">
+        <v>743246593</v>
+      </c>
       <c r="D33" s="130" t="n">
         <v>17000</v>
       </c>
       <c r="E33" s="130"/>
-      <c r="F33" s="153"/>
+      <c r="F33" s="159" t="n">
+        <v>17000</v>
+      </c>
       <c r="G33" s="130" t="n">
         <v>250</v>
       </c>
@@ -10428,8 +10607,10 @@
         <v>250</v>
       </c>
       <c r="I33" s="79"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J33" s="148"/>
+      <c r="K33" s="152"/>
+    </row>
+    <row r="34" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="87" t="s">
         <v>72</v>
       </c>
@@ -10441,14 +10622,20 @@
         <v>12000</v>
       </c>
       <c r="E34" s="118"/>
-      <c r="F34" s="151"/>
+      <c r="F34" s="156" t="n">
+        <v>12000</v>
+      </c>
       <c r="G34" s="118" t="n">
         <v>250</v>
       </c>
-      <c r="H34" s="118"/>
+      <c r="H34" s="118" t="n">
+        <v>250</v>
+      </c>
       <c r="I34" s="87"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J34" s="148"/>
+      <c r="K34" s="152"/>
+    </row>
+    <row r="35" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="79" t="s">
         <v>74</v>
       </c>
@@ -10462,14 +10649,16 @@
         <v>12000</v>
       </c>
       <c r="E35" s="130"/>
-      <c r="F35" s="153"/>
-      <c r="G35" s="130" t="n">
-        <v>250</v>
-      </c>
+      <c r="F35" s="159"/>
+      <c r="G35" s="130"/>
       <c r="H35" s="130"/>
       <c r="I35" s="79"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J35" s="148"/>
+      <c r="K35" s="152" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="79" t="s">
         <v>76</v>
       </c>
@@ -10483,14 +10672,20 @@
         <v>12000</v>
       </c>
       <c r="E36" s="130"/>
-      <c r="F36" s="153"/>
+      <c r="F36" s="159" t="n">
+        <v>12500</v>
+      </c>
       <c r="G36" s="130" t="n">
         <v>250</v>
       </c>
-      <c r="H36" s="130"/>
+      <c r="H36" s="130" t="n">
+        <v>250</v>
+      </c>
       <c r="I36" s="79"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J36" s="148"/>
+      <c r="K36" s="152"/>
+    </row>
+    <row r="37" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="79" t="s">
         <v>77</v>
       </c>
@@ -10504,7 +10699,7 @@
         <v>12000</v>
       </c>
       <c r="E37" s="130"/>
-      <c r="F37" s="153" t="n">
+      <c r="F37" s="159" t="n">
         <v>17000</v>
       </c>
       <c r="G37" s="130" t="n">
@@ -10514,13 +10709,14 @@
         <v>250</v>
       </c>
       <c r="I37" s="79" t="s">
-        <v>133</v>
-      </c>
-      <c r="J37" s="152" t="n">
+        <v>135</v>
+      </c>
+      <c r="J37" s="157" t="n">
         <v>45755</v>
       </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K37" s="152"/>
+    </row>
+    <row r="38" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="79" t="s">
         <v>79</v>
       </c>
@@ -10534,14 +10730,20 @@
         <v>12500</v>
       </c>
       <c r="E38" s="130"/>
-      <c r="F38" s="154"/>
+      <c r="F38" s="160" t="n">
+        <v>12500</v>
+      </c>
       <c r="G38" s="134" t="n">
         <v>250</v>
       </c>
-      <c r="H38" s="135"/>
+      <c r="H38" s="135" t="n">
+        <v>250</v>
+      </c>
       <c r="I38" s="79"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J38" s="148"/>
+      <c r="K38" s="152"/>
+    </row>
+    <row r="39" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="98" t="s">
         <v>81</v>
       </c>
@@ -10555,7 +10757,7 @@
         <v>12000</v>
       </c>
       <c r="E39" s="137"/>
-      <c r="F39" s="155"/>
+      <c r="F39" s="161"/>
       <c r="G39" s="137" t="n">
         <v>250</v>
       </c>
@@ -10563,8 +10765,10 @@
       <c r="I39" s="98" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J39" s="148"/>
+      <c r="K39" s="152"/>
+    </row>
+    <row r="40" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="79" t="s">
         <v>83</v>
       </c>
@@ -10578,7 +10782,9 @@
         <v>12500</v>
       </c>
       <c r="E40" s="130"/>
-      <c r="F40" s="153"/>
+      <c r="F40" s="159" t="n">
+        <v>12500</v>
+      </c>
       <c r="G40" s="130" t="n">
         <v>250</v>
       </c>
@@ -10586,8 +10792,10 @@
         <v>250</v>
       </c>
       <c r="I40" s="79"/>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J40" s="148"/>
+      <c r="K40" s="152"/>
+    </row>
+    <row r="41" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="79" t="s">
         <v>84</v>
       </c>
@@ -10601,7 +10809,9 @@
         <v>17500</v>
       </c>
       <c r="E41" s="130"/>
-      <c r="F41" s="153"/>
+      <c r="F41" s="159" t="n">
+        <v>17500</v>
+      </c>
       <c r="G41" s="130" t="n">
         <v>250</v>
       </c>
@@ -10609,8 +10819,10 @@
         <v>250</v>
       </c>
       <c r="I41" s="79"/>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J41" s="148"/>
+      <c r="K41" s="152"/>
+    </row>
+    <row r="42" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="79" t="s">
         <v>86</v>
       </c>
@@ -10624,7 +10836,9 @@
         <v>18000</v>
       </c>
       <c r="E42" s="130"/>
-      <c r="F42" s="153"/>
+      <c r="F42" s="159" t="n">
+        <v>18000</v>
+      </c>
       <c r="G42" s="130" t="n">
         <v>250</v>
       </c>
@@ -10632,8 +10846,10 @@
         <v>250</v>
       </c>
       <c r="I42" s="79"/>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J42" s="148"/>
+      <c r="K42" s="152"/>
+    </row>
+    <row r="43" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="79"/>
       <c r="B43" s="130"/>
       <c r="C43" s="130"/>
@@ -10641,9 +10857,9 @@
         <v>455250</v>
       </c>
       <c r="E43" s="138"/>
-      <c r="F43" s="156" t="n">
+      <c r="F43" s="162" t="n">
         <f aca="false">SUM(F7:F42)</f>
-        <v>90000</v>
+        <v>381000</v>
       </c>
       <c r="G43" s="138" t="n">
         <v>8000</v>
@@ -10652,6 +10868,11 @@
         <v>4250</v>
       </c>
       <c r="I43" s="79"/>
+      <c r="J43" s="148"/>
+      <c r="K43" s="152" t="n">
+        <f aca="false">SUM(K7:K42)</f>
+        <v>44000</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D44" s="139"/>

--- a/PROPERTIES/SHANAYA/SHANAYA 2025.xlsx
+++ b/PROPERTIES/SHANAYA/SHANAYA 2025.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="964" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="965" uniqueCount="138">
   <si>
     <t xml:space="preserve">COURTLAND REALTORS LTD P.O.BOX 11993, NAIROBI</t>
   </si>
@@ -435,6 +435,12 @@
   </si>
   <si>
     <t xml:space="preserve">TH40WHXXGE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MGNT COMM 4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LANDLORD AMOUNT</t>
   </si>
 </sst>
 </file>
@@ -450,7 +456,7 @@
     <numFmt numFmtId="169" formatCode="#,##0"/>
     <numFmt numFmtId="170" formatCode="mm/dd/yy"/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="33">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -689,6 +695,12 @@
       <family val="1"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="1"/>
+      <name val="Georgia"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -773,7 +785,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="163">
+  <cellXfs count="164">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1423,6 +1435,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9781,7 +9797,7 @@
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="78" width="8.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="78" width="26.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="78" width="29.81"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="78" width="17.22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="78" width="11.56"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="78" width="31.76"/>
@@ -9963,9 +9979,15 @@
         <v>10000</v>
       </c>
       <c r="E9" s="89"/>
-      <c r="F9" s="151"/>
-      <c r="G9" s="97"/>
-      <c r="H9" s="97"/>
+      <c r="F9" s="151" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G9" s="97" t="n">
+        <v>250</v>
+      </c>
+      <c r="H9" s="97" t="n">
+        <v>250</v>
+      </c>
       <c r="I9" s="93"/>
       <c r="J9" s="148"/>
       <c r="K9" s="152" t="n">
@@ -9980,9 +10002,7 @@
         <v>21</v>
       </c>
       <c r="C10" s="100"/>
-      <c r="D10" s="101" t="n">
-        <v>13000</v>
-      </c>
+      <c r="D10" s="101"/>
       <c r="E10" s="102"/>
       <c r="F10" s="153"/>
       <c r="G10" s="103"/>
@@ -10028,9 +10048,7 @@
         <v>26</v>
       </c>
       <c r="C12" s="107"/>
-      <c r="D12" s="108" t="n">
-        <v>11000</v>
-      </c>
+      <c r="D12" s="108"/>
       <c r="E12" s="108"/>
       <c r="F12" s="154"/>
       <c r="G12" s="108"/>
@@ -10052,11 +10070,11 @@
         <v>768169176</v>
       </c>
       <c r="D13" s="89" t="n">
-        <v>11000</v>
+        <v>10000</v>
       </c>
       <c r="E13" s="111"/>
       <c r="F13" s="150" t="n">
-        <v>11000</v>
+        <v>10000</v>
       </c>
       <c r="G13" s="89" t="n">
         <v>250</v>
@@ -10077,11 +10095,11 @@
         <v>711926938</v>
       </c>
       <c r="D14" s="114" t="n">
-        <v>16000</v>
+        <v>15000</v>
       </c>
       <c r="E14" s="114"/>
       <c r="F14" s="155" t="n">
-        <v>16000</v>
+        <v>15000</v>
       </c>
       <c r="G14" s="114" t="n">
         <v>250</v>
@@ -10101,9 +10119,7 @@
         <v>18</v>
       </c>
       <c r="C15" s="113"/>
-      <c r="D15" s="114" t="n">
-        <v>10000</v>
-      </c>
+      <c r="D15" s="114"/>
       <c r="E15" s="114"/>
       <c r="F15" s="155"/>
       <c r="G15" s="114"/>
@@ -10260,7 +10276,7 @@
         <v>700278925</v>
       </c>
       <c r="D21" s="97" t="n">
-        <v>12500</v>
+        <v>12000</v>
       </c>
       <c r="E21" s="118"/>
       <c r="F21" s="151" t="n">
@@ -10291,8 +10307,12 @@
       <c r="F22" s="150" t="n">
         <v>12000</v>
       </c>
-      <c r="G22" s="89"/>
-      <c r="H22" s="89"/>
+      <c r="G22" s="89" t="n">
+        <v>250</v>
+      </c>
+      <c r="H22" s="89" t="n">
+        <v>250</v>
+      </c>
       <c r="I22" s="91"/>
       <c r="J22" s="148"/>
       <c r="K22" s="152"/>
@@ -10312,7 +10332,7 @@
       </c>
       <c r="E23" s="114"/>
       <c r="F23" s="155" t="n">
-        <v>17500</v>
+        <v>17000</v>
       </c>
       <c r="G23" s="114" t="n">
         <v>250</v>
@@ -10374,7 +10394,7 @@
       </c>
       <c r="E25" s="125"/>
       <c r="F25" s="155" t="n">
-        <v>12500</v>
+        <v>12000</v>
       </c>
       <c r="G25" s="125" t="n">
         <v>250</v>
@@ -10401,7 +10421,7 @@
         <v>742242625</v>
       </c>
       <c r="D26" s="114" t="n">
-        <v>12000</v>
+        <v>6000</v>
       </c>
       <c r="E26" s="128"/>
       <c r="F26" s="155" t="n">
@@ -10432,7 +10452,7 @@
       </c>
       <c r="E27" s="89"/>
       <c r="F27" s="150" t="n">
-        <v>12500</v>
+        <v>12000</v>
       </c>
       <c r="G27" s="89" t="n">
         <v>250</v>
@@ -10459,11 +10479,11 @@
         <v>705296435</v>
       </c>
       <c r="D28" s="114" t="n">
-        <v>12500</v>
+        <v>12000</v>
       </c>
       <c r="E28" s="114"/>
       <c r="F28" s="155" t="n">
-        <v>12500</v>
+        <v>12000</v>
       </c>
       <c r="G28" s="114" t="n">
         <v>250</v>
@@ -10490,7 +10510,7 @@
       </c>
       <c r="E29" s="114"/>
       <c r="F29" s="150" t="n">
-        <v>12500</v>
+        <v>12000</v>
       </c>
       <c r="G29" s="89" t="n">
         <v>250</v>
@@ -10538,11 +10558,11 @@
         <v>721919440</v>
       </c>
       <c r="D31" s="131" t="n">
-        <v>13000</v>
+        <v>12000</v>
       </c>
       <c r="E31" s="89"/>
       <c r="F31" s="159" t="n">
-        <v>12500</v>
+        <v>12000</v>
       </c>
       <c r="G31" s="130" t="n">
         <v>250</v>
@@ -10673,7 +10693,7 @@
       </c>
       <c r="E36" s="130"/>
       <c r="F36" s="159" t="n">
-        <v>12500</v>
+        <v>12000</v>
       </c>
       <c r="G36" s="130" t="n">
         <v>250</v>
@@ -10727,11 +10747,11 @@
         <v>703211387</v>
       </c>
       <c r="D38" s="130" t="n">
-        <v>12500</v>
+        <v>12000</v>
       </c>
       <c r="E38" s="130"/>
       <c r="F38" s="160" t="n">
-        <v>12500</v>
+        <v>12000</v>
       </c>
       <c r="G38" s="134" t="n">
         <v>250</v>
@@ -10753,14 +10773,10 @@
       <c r="C39" s="137" t="n">
         <v>729808848</v>
       </c>
-      <c r="D39" s="137" t="n">
-        <v>12000</v>
-      </c>
+      <c r="D39" s="137"/>
       <c r="E39" s="137"/>
       <c r="F39" s="161"/>
-      <c r="G39" s="137" t="n">
-        <v>250</v>
-      </c>
+      <c r="G39" s="137"/>
       <c r="H39" s="137"/>
       <c r="I39" s="98" t="s">
         <v>82</v>
@@ -10779,11 +10795,11 @@
         <v>722648411</v>
       </c>
       <c r="D40" s="130" t="n">
-        <v>12500</v>
+        <v>12000</v>
       </c>
       <c r="E40" s="130"/>
       <c r="F40" s="159" t="n">
-        <v>12500</v>
+        <v>12000</v>
       </c>
       <c r="G40" s="130" t="n">
         <v>250</v>
@@ -10806,11 +10822,11 @@
         <v>727104429</v>
       </c>
       <c r="D41" s="130" t="n">
-        <v>17500</v>
+        <v>17000</v>
       </c>
       <c r="E41" s="130"/>
       <c r="F41" s="159" t="n">
-        <v>17500</v>
+        <v>17000</v>
       </c>
       <c r="G41" s="130" t="n">
         <v>250</v>
@@ -10833,11 +10849,11 @@
         <v>757112245</v>
       </c>
       <c r="D42" s="130" t="n">
-        <v>18000</v>
+        <v>17000</v>
       </c>
       <c r="E42" s="130"/>
       <c r="F42" s="159" t="n">
-        <v>18000</v>
+        <v>17000</v>
       </c>
       <c r="G42" s="130" t="n">
         <v>250</v>
@@ -10854,12 +10870,13 @@
       <c r="B43" s="130"/>
       <c r="C43" s="130"/>
       <c r="D43" s="138" t="n">
-        <v>455250</v>
+        <f aca="false">SUM(D7:D42)</f>
+        <v>400000</v>
       </c>
       <c r="E43" s="138"/>
       <c r="F43" s="162" t="n">
         <f aca="false">SUM(F7:F42)</f>
-        <v>381000</v>
+        <v>383000</v>
       </c>
       <c r="G43" s="138" t="n">
         <v>8000</v>
@@ -10909,7 +10926,9 @@
       <c r="B48" s="78" t="s">
         <v>123</v>
       </c>
-      <c r="D48" s="140"/>
+      <c r="D48" s="140" t="n">
+        <v>410000</v>
+      </c>
       <c r="E48" s="141"/>
       <c r="F48" s="140"/>
       <c r="G48" s="140"/>
@@ -10936,26 +10955,45 @@
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="78" t="s">
-        <v>126</v>
+        <v>136</v>
+      </c>
+      <c r="C53" s="163" t="n">
+        <v>18210</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="78" t="s">
         <v>92</v>
       </c>
+      <c r="C54" s="78" t="n">
+        <v>3000</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="78" t="s">
         <v>90</v>
       </c>
+      <c r="C55" s="78" t="n">
+        <v>6000</v>
+      </c>
       <c r="E55" s="143"/>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="78" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="C56" s="78" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B57" s="78" t="s">
+        <v>137</v>
+      </c>
+      <c r="C57" s="78" t="n">
+        <v>367790</v>
+      </c>
+    </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
